--- a/data/trans_dic/P43C-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Estudios-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>40,61%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>53,44%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51,42%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>47,23%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,98; 43,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,4; 56,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,12; 54,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,14; 50,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,88; 43,32</t>
+          <t>37,98; 43,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,44; 55,95</t>
+          <t>50,4; 56,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,09; 55,04</t>
+          <t>48,12; 54,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,34; 50,71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>37,88; 43,32</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50,44; 55,95</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>48,09; 55,04</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,34; 50,71</t>
+          <t>44,14; 50,51</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>53,79%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60,12%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>66,28%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>53,79%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>57,69; 62,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68,68; 73,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,18; 68,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,34; 62,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,83; 62,48</t>
+          <t>57,69; 62,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,97; 73,23</t>
+          <t>68,68; 73,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,11; 68,47</t>
+          <t>64,18; 68,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,18; 62,42</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>57,83; 62,48</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68,97; 73,23</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>64,11; 68,47</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>36,18; 62,42</t>
+          <t>34,34; 62,56</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>75,37%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>76,2%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>77,51%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>75,37%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,38; 72,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72,06; 80,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>73,75; 80,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,43; 78,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,16; 72,84</t>
+          <t>64,38; 72,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,73; 80,09</t>
+          <t>72,06; 80,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,02; 81,2</t>
+          <t>73,75; 80,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,75; 79,18</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>64,16; 72,84</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>71,73; 80,09</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>74,02; 81,2</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>71,75; 79,18</t>
+          <t>71,43; 78,93</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>53,81%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>65,09%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>63,88%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,92%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,07; 55,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,51; 66,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,21; 65,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,87; 61,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,98; 55,46</t>
+          <t>52,07; 55,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,49; 66,86</t>
+          <t>63,51; 66,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,21; 65,54</t>
+          <t>62,21; 65,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,26; 61,3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>51,98; 55,46</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>63,49; 66,86</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>62,21; 65,54</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>43,26; 61,3</t>
+          <t>41,87; 61,28</t>
         </is>
       </c>
     </row>
@@ -1204,15 +1008,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1224,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1237,22 +1040,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,20 +1059,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1314,26 +1105,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1350,10 +1121,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1368,22 +1135,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>522</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>658</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1402,26 +1169,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>532</t>
         </is>
@@ -1436,22 +1183,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>521304</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>704584</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>502579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1470,26 +1217,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>285746</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>521304</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>704584</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>502579</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>285746</t>
         </is>
@@ -1504,62 +1231,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>487539; 557534</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>664456; 739377</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>470322; 536415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>267050; 305588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>486338; 556093</t>
+          <t>487539; 557534</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>665022; 737574</t>
+          <t>664456; 739377</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>470096; 537984</t>
+          <t>470322; 536415</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>268250; 306767</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>486338; 556093</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>665022; 737574</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>470096; 537984</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>268250; 306767</t>
+          <t>267050; 305588</t>
         </is>
       </c>
     </row>
@@ -1576,22 +1283,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>913</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1610,26 +1317,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>913</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1136</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1338</t>
         </is>
@@ -1644,22 +1331,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944675</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1237529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1306182</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>935424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1678,26 +1365,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>935424</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>944675</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1237529</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1306182</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>935424</t>
         </is>
@@ -1712,62 +1379,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>906391; 981937</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1197328; 1273448</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1264784; 1349395</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>597162; 1087995</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>908653; 981723</t>
+          <t>906391; 981937</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1202368; 1276610</t>
+          <t>1197328; 1273448</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1263487; 1349340</t>
+          <t>1264784; 1349395</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>629192; 1085539</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>908653; 981723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1202368; 1276610</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1263487; 1349340</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>629192; 1085539</t>
+          <t>597162; 1087995</t>
         </is>
       </c>
     </row>
@@ -1784,22 +1431,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>310</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>401</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1818,26 +1465,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>543</t>
         </is>
@@ -1852,22 +1479,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324369</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347893</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1886,26 +1513,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>346682</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>324369</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>347893</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>424088</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>346682</t>
         </is>
@@ -1920,62 +1527,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>303832; 342733</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>329006; 366523</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>403495; 442763</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>328585; 363047</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>302810; 343807</t>
+          <t>303832; 342733</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>327496; 365683</t>
+          <t>329006; 366523</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>404977; 444256</t>
+          <t>403495; 442763</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>330026; 364195</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>302810; 343807</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>327496; 365683</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>404977; 444256</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>330026; 364195</t>
+          <t>328585; 363047</t>
         </is>
       </c>
     </row>
@@ -1992,22 +1579,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2026,26 +1613,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2413</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2413</t>
         </is>
@@ -2060,22 +1627,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1790349</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2290006</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2232850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1567852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2094,26 +1661,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1567852</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1790349</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2290006</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2232850</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1567852</t>
         </is>
@@ -2128,62 +1675,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1732279; 1846842</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2234574; 2352384</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2174460; 2289704</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1174074; 1718188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1729293; 1845045</t>
+          <t>1732279; 1846842</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2233729; 2352220</t>
+          <t>2234574; 2352384</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2174260; 2290815</t>
+          <t>2174460; 2289704</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1213073; 1718825</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>1729293; 1845045</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2233729; 2352220</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2174260; 2290815</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>1213073; 1718825</t>
+          <t>1174074; 1718188</t>
         </is>
       </c>
     </row>
@@ -2195,14 +1722,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P43C-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Estudios-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,98; 43,43</t>
+          <t>38,08; 43,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,4; 56,08</t>
+          <t>50,63; 56,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,12; 54,88</t>
+          <t>47,99; 54,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,14; 50,51</t>
+          <t>43,04; 49,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,98; 43,43</t>
+          <t>38,08; 43,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,4; 56,08</t>
+          <t>50,63; 56,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,12; 54,88</t>
+          <t>47,99; 54,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,14; 50,51</t>
+          <t>43,04; 49,28</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,69; 62,49</t>
+          <t>57,55; 62,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,68; 73,05</t>
+          <t>68,78; 73,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,18; 68,47</t>
+          <t>64,11; 68,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,34; 62,56</t>
+          <t>54,9; 59,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,69; 62,49</t>
+          <t>57,55; 62,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,68; 73,05</t>
+          <t>68,78; 73,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,18; 68,47</t>
+          <t>64,11; 68,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,34; 62,56</t>
+          <t>54,9; 59,52</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,87%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,38; 72,62</t>
+          <t>64,46; 73,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,06; 80,28</t>
+          <t>71,74; 80,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,75; 80,92</t>
+          <t>73,68; 80,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,43; 78,93</t>
+          <t>72,21; 79,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,38; 72,62</t>
+          <t>64,46; 73,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,06; 80,28</t>
+          <t>71,74; 80,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,75; 80,92</t>
+          <t>73,68; 80,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,43; 78,93</t>
+          <t>72,21; 79,42</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,07; 55,51</t>
+          <t>51,94; 55,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,51; 66,86</t>
+          <t>63,52; 66,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,21; 65,51</t>
+          <t>62,14; 65,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41,87; 61,28</t>
+          <t>56,23; 59,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,07; 55,51</t>
+          <t>51,94; 55,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,51; 66,86</t>
+          <t>63,52; 66,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,21; 65,51</t>
+          <t>62,14; 65,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,87; 61,28</t>
+          <t>56,23; 59,55</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>285746</t>
+          <t>303739</t>
         </is>
       </c>
     </row>
@@ -1231,42 +1231,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>487539; 557534</t>
+          <t>488857; 557364</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>664456; 739377</t>
+          <t>667543; 742918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>470322; 536415</t>
+          <t>469029; 534609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267050; 305588</t>
+          <t>283700; 324867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>487539; 557534</t>
+          <t>488857; 557364</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>664456; 739377</t>
+          <t>667543; 742918</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>470322; 536415</t>
+          <t>469029; 534609</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>267050; 305588</t>
+          <t>283700; 324867</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>935424</t>
+          <t>916008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>935424</t>
+          <t>916008</t>
         </is>
       </c>
     </row>
@@ -1379,42 +1379,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>906391; 981937</t>
+          <t>904195; 983552</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1197328; 1273448</t>
+          <t>1199087; 1273126</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1264784; 1349395</t>
+          <t>1263364; 1349156</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>597162; 1087995</t>
+          <t>882092; 956316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>906391; 981937</t>
+          <t>904195; 983552</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1197328; 1273448</t>
+          <t>1199087; 1273126</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1264784; 1349395</t>
+          <t>1263364; 1349156</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>597162; 1087995</t>
+          <t>882092; 956316</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386803</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>346682</t>
+          <t>386803</t>
         </is>
       </c>
     </row>
@@ -1527,42 +1527,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>303832; 342733</t>
+          <t>304218; 345113</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>329006; 366523</t>
+          <t>327521; 365800</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>403495; 442763</t>
+          <t>403145; 441073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>328585; 363047</t>
+          <t>368121; 404879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>303832; 342733</t>
+          <t>304218; 345113</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>329006; 366523</t>
+          <t>327521; 365800</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>403495; 442763</t>
+          <t>403145; 441073</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>328585; 363047</t>
+          <t>368121; 404879</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1567852</t>
+          <t>1606551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1567852</t>
+          <t>1606551</t>
         </is>
       </c>
     </row>
@@ -1675,42 +1675,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1732279; 1846842</t>
+          <t>1728222; 1846242</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2234574; 2352384</t>
+          <t>2234860; 2344940</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2174460; 2289704</t>
+          <t>2171925; 2288415</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1174074; 1718188</t>
+          <t>1560800; 1652936</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1732279; 1846842</t>
+          <t>1728222; 1846242</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2234574; 2352384</t>
+          <t>2234860; 2344940</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2174460; 2289704</t>
+          <t>2171925; 2288415</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1174074; 1718188</t>
+          <t>1560800; 1652936</t>
         </is>
       </c>
     </row>
